--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -471,7 +471,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.08630369985580444</v>
+        <v>0.02438655026406922</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3123156471855663</v>
+        <v>0.1723701178791144</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.4074815262926133</v>
+        <v>0.157411035990932</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5891792691883648</v>
+        <v>0.2219560196814252</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.231639118178226</v>
+        <v>0.09812044708837497</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.4233359704652703</v>
+        <v>0.2813000596522671</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>48.43630125868315</v>
+        <v>20.26984647591101</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.4696970446894342</v>
+        <v>-0.2819470013006294</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2658031294060726</v>
+        <v>0.2962092751392976</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-2.404989435323399</v>
+        <v>-1.066228603782279</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-3.018521839391758</v>
+        <v>-1.443523077881216</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4879321801655778</v>
+        <v>0.2888776031683397</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9907447512584918</v>
+        <v>-1.009796682989607</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>55.36577063643931</v>
+        <v>40.44004777906486</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1231161162032542</v>
+        <v>-0.1970615863514513</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2367832002408323</v>
+        <v>0.2366834185379364</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.5224266545163877</v>
+        <v>-0.9099268242978753</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.7304717659571102</v>
+        <v>-1.215516123539265</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2914806573064712</v>
+        <v>0.2472661621288711</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.4386698621330102</v>
+        <v>-0.8262786889544181</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>55.15680352941332</v>
+        <v>48.89226852345326</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.004127321944094042</v>
+        <v>0.01319235548461384</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2690149190179742</v>
+        <v>0.3722754272877942</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.09180414873400544</v>
+        <v>0.1805983890672971</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.1543804846011322</v>
+        <v>0.2711522994452807</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2218818073861858</v>
+        <v>0.2153785432383257</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.01937174799504656</v>
+        <v>0.06380033344842004</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>58.62857560022527</v>
+        <v>53.71493324696652</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1151464128999449</v>
+        <v>0.150282397387578</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2652981628773033</v>
+        <v>0.2937000914472565</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.503431522725314</v>
+        <v>0.5914999313062581</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.6826482293730621</v>
+        <v>0.817405303670887</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.202768701243051</v>
+        <v>0.2971256061567153</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.5901147773879939</v>
+        <v>0.5259143998619399</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>59.78660089615332</v>
+        <v>65.65627493957304</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1300600293828289</v>
+        <v>0.5195021323449358</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3186450823337562</v>
+        <v>0.4215345180091976</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8076047257899495</v>
+        <v>1.975497419508096</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.172393290200501</v>
+        <v>3.116159631731529</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1911304906456232</v>
+        <v>0.1285901842808549</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.298381623845723</v>
+        <v>8.82715740482989</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>49.35145984702233</v>
+        <v>40.69511340588503</v>
       </c>
     </row>
   </sheetData>
